--- a/input/13_Incentives.xlsx
+++ b/input/13_Incentives.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_A5CF89AD79EA3F1948E510020BE435FF3CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{147D63D2-BDF9-4EC9-8D94-EDE19071BAC2}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/input/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_A5CF89AD79EA3F1948E510020BE435FF3CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{645AFAAD-C96A-47D1-8965-BF65C73B376F}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="measure_level" sheetId="1" r:id="rId1"/>
@@ -33,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="94">
-  <si>
-    <t>condition_name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="89">
   <si>
     <t>electric_incentive_percentage</t>
   </si>
@@ -47,51 +49,6 @@
     <t>nonutility_incentive_percentage</t>
   </si>
   <si>
-    <t>furnace_fuel_oil_existing_residential</t>
-  </si>
-  <si>
-    <t>furnace_natural_gas_baseline_residential</t>
-  </si>
-  <si>
-    <t>furnace_natural_gas_efficient_residential</t>
-  </si>
-  <si>
-    <t>room_ac_electricity_baseline_residential</t>
-  </si>
-  <si>
-    <t>room_ac_electricity_efficient_residential</t>
-  </si>
-  <si>
-    <t>air_conditioner_electricity_baseline_residential</t>
-  </si>
-  <si>
-    <t>air_conditioner_electricity_efficient_residential</t>
-  </si>
-  <si>
-    <t>cchp_electricity_efficient_residential</t>
-  </si>
-  <si>
-    <t>refrigerator_electricity_existing_residential</t>
-  </si>
-  <si>
-    <t>refrigerator_electricity_baseline_residential</t>
-  </si>
-  <si>
-    <t>refrigerator_electricity_efficient_residential</t>
-  </si>
-  <si>
-    <t>refrigerator_electricity_top10_residential</t>
-  </si>
-  <si>
-    <t>whole_home_insultation_existing_residential</t>
-  </si>
-  <si>
-    <t>whole_home_insultation_baseline_residential</t>
-  </si>
-  <si>
-    <t>whole_home_insultation_efficient_residential</t>
-  </si>
-  <si>
     <t>Program potential</t>
   </si>
   <si>
@@ -315,13 +272,46 @@
   </si>
   <si>
     <t>Large Warehouse</t>
+  </si>
+  <si>
+    <t>refrigerator_electricity_efficient_residential_refrigerator_electricity_existing_residential</t>
+  </si>
+  <si>
+    <t>refrigerator_electricity_efficient_residential_refrigerator_electricity_baseline_residential</t>
+  </si>
+  <si>
+    <t>refrigerator_electricity_top10_residential_refrigerator_electricity_existing_residential</t>
+  </si>
+  <si>
+    <t>refrigerator_electricity_top10_residential_refrigerator_electricity_baseline_residential</t>
+  </si>
+  <si>
+    <t>insulation_natural_gas_efficient_residential_whole_home_natural_gas_baseline_residential</t>
+  </si>
+  <si>
+    <t>HERS_electricity_efficient_residential_whole_home_natural_gas_baseline_residential</t>
+  </si>
+  <si>
+    <t>Measure_name</t>
+  </si>
+  <si>
+    <t>utility</t>
+  </si>
+  <si>
+    <t>test_utility_1</t>
+  </si>
+  <si>
+    <t>test_utility_2</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,8 +336,9 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -392,11 +383,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -732,236 +731,2085 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F115"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="1" max="1" width="81.7109375" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="57.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>0.5</v>
-      </c>
-      <c r="C2">
-        <v>0.5</v>
-      </c>
-      <c r="D2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>0.5</v>
-      </c>
-      <c r="C3">
-        <v>0.5</v>
-      </c>
-      <c r="D3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>0.5</v>
-      </c>
-      <c r="C4">
-        <v>0.5</v>
-      </c>
-      <c r="D4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>0.5</v>
-      </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>0.5</v>
-      </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
-      <c r="D6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>0.5</v>
-      </c>
-      <c r="C7">
-        <v>0.5</v>
-      </c>
-      <c r="D7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>0.5</v>
-      </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
-      <c r="D8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>0.5</v>
-      </c>
-      <c r="C9">
-        <v>0.5</v>
-      </c>
-      <c r="D9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>0.5</v>
-      </c>
-      <c r="C10">
-        <v>0.5</v>
-      </c>
-      <c r="D10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>0.5</v>
-      </c>
-      <c r="C11">
-        <v>0.5</v>
-      </c>
-      <c r="D11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12">
-        <v>0.5</v>
-      </c>
-      <c r="C12">
-        <v>0.5</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
-        <v>0.5</v>
-      </c>
-      <c r="C13">
-        <v>0.5</v>
-      </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>0.5</v>
-      </c>
-      <c r="C14">
-        <v>0.5</v>
-      </c>
-      <c r="D14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15">
-        <v>0.5</v>
-      </c>
-      <c r="C15">
-        <v>0.5</v>
-      </c>
-      <c r="D15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
-        <v>0.5</v>
-      </c>
-      <c r="C16">
-        <v>0.5</v>
-      </c>
-      <c r="D16">
-        <v>0.5</v>
-      </c>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D47" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D48" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D49" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E49" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C51" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D51" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E51" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D52" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E54" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E57" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D59" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D60" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C61" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E61" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D62" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D63" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E64" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D66" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D67" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D68" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D69" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E69" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D70" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E70" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C71" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D71" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E71" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C72" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D72" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E72" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C73" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D73" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E73" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C74" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D74" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E74" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D75" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E75" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C76" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D76" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D77" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E77" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="4">
+        <v>0</v>
+      </c>
+      <c r="D78" s="4">
+        <v>0</v>
+      </c>
+      <c r="E78" s="4">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="4">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="4">
+        <v>0</v>
+      </c>
+      <c r="D80" s="4">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="4">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="4">
+        <v>0</v>
+      </c>
+      <c r="D82" s="4">
+        <v>0</v>
+      </c>
+      <c r="E82" s="4">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" s="4">
+        <v>0</v>
+      </c>
+      <c r="D83" s="4">
+        <v>0</v>
+      </c>
+      <c r="E83" s="4">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" s="4">
+        <v>0</v>
+      </c>
+      <c r="D84" s="4">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C85" s="4">
+        <v>0</v>
+      </c>
+      <c r="D85" s="4">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C86" s="4">
+        <v>0</v>
+      </c>
+      <c r="D86" s="4">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87" s="4">
+        <v>0</v>
+      </c>
+      <c r="D87" s="4">
+        <v>0</v>
+      </c>
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" s="4">
+        <v>0</v>
+      </c>
+      <c r="D88" s="4">
+        <v>0</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C89" s="4">
+        <v>0</v>
+      </c>
+      <c r="D89" s="4">
+        <v>0</v>
+      </c>
+      <c r="E89" s="4">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" s="4">
+        <v>0</v>
+      </c>
+      <c r="D90" s="4">
+        <v>0</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C91" s="4">
+        <v>0</v>
+      </c>
+      <c r="D91" s="4">
+        <v>0</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C92" s="4">
+        <v>0</v>
+      </c>
+      <c r="D92" s="4">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C93" s="4">
+        <v>0</v>
+      </c>
+      <c r="D93" s="4">
+        <v>0</v>
+      </c>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94" s="4">
+        <v>0</v>
+      </c>
+      <c r="D94" s="4">
+        <v>0</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C95" s="4">
+        <v>0</v>
+      </c>
+      <c r="D95" s="4">
+        <v>0</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C96" s="4">
+        <v>0</v>
+      </c>
+      <c r="D96" s="4">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C97" s="4">
+        <v>0</v>
+      </c>
+      <c r="D97" s="4">
+        <v>0</v>
+      </c>
+      <c r="E97" s="4">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C98" s="4">
+        <v>0</v>
+      </c>
+      <c r="D98" s="4">
+        <v>0</v>
+      </c>
+      <c r="E98" s="4">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C99" s="4">
+        <v>0</v>
+      </c>
+      <c r="D99" s="4">
+        <v>0</v>
+      </c>
+      <c r="E99" s="4">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C100" s="4">
+        <v>0</v>
+      </c>
+      <c r="D100" s="4">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="4">
+        <v>0</v>
+      </c>
+      <c r="D101" s="4">
+        <v>0</v>
+      </c>
+      <c r="E101" s="4">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C102" s="4">
+        <v>0</v>
+      </c>
+      <c r="D102" s="4">
+        <v>0</v>
+      </c>
+      <c r="E102" s="4">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C103" s="4">
+        <v>0</v>
+      </c>
+      <c r="D103" s="4">
+        <v>0</v>
+      </c>
+      <c r="E103" s="4">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C104" s="4">
+        <v>0</v>
+      </c>
+      <c r="D104" s="4">
+        <v>0</v>
+      </c>
+      <c r="E104" s="4">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C105" s="4">
+        <v>0</v>
+      </c>
+      <c r="D105" s="4">
+        <v>0</v>
+      </c>
+      <c r="E105" s="4">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" s="4">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C107" s="4">
+        <v>0</v>
+      </c>
+      <c r="D107" s="4">
+        <v>0</v>
+      </c>
+      <c r="E107" s="4">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C108" s="4">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4">
+        <v>0</v>
+      </c>
+      <c r="E108" s="4">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C109" s="4">
+        <v>0</v>
+      </c>
+      <c r="D109" s="4">
+        <v>0</v>
+      </c>
+      <c r="E109" s="4">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4"/>
+    </row>
+    <row r="110" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="4">
+        <v>0</v>
+      </c>
+      <c r="D110" s="4">
+        <v>0</v>
+      </c>
+      <c r="E110" s="4">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4"/>
+    </row>
+    <row r="111" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C111" s="4">
+        <v>0</v>
+      </c>
+      <c r="D111" s="4">
+        <v>0</v>
+      </c>
+      <c r="E111" s="4">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4"/>
+    </row>
+    <row r="112" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" s="4">
+        <v>0</v>
+      </c>
+      <c r="D112" s="4">
+        <v>0</v>
+      </c>
+      <c r="E112" s="4">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C113" s="4">
+        <v>0</v>
+      </c>
+      <c r="D113" s="4">
+        <v>0</v>
+      </c>
+      <c r="E113" s="4">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="4">
+        <v>0</v>
+      </c>
+      <c r="D114" s="4">
+        <v>0</v>
+      </c>
+      <c r="E114" s="4">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C115" s="4">
+        <v>0</v>
+      </c>
+      <c r="D115" s="4">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -971,21 +2819,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F49822-C788-4AB4-AC26-E2B70E42F89A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0.5</v>
       </c>
@@ -993,9 +2841,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1006,7 +2854,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{833A06F8-4920-4877-8B5F-342B370A27B4}">
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -1016,50 +2864,50 @@
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="M1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1068,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1077,7 +2925,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1086,18 +2934,18 @@
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="O2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1106,7 +2954,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1115,7 +2963,7 @@
         <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1124,18 +2972,18 @@
         <v>2</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="O3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1144,7 +2992,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1153,7 +3001,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1162,18 +3010,18 @@
         <v>3</v>
       </c>
       <c r="N4" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="O4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1182,7 +3030,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1191,7 +3039,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1200,18 +3048,18 @@
         <v>4</v>
       </c>
       <c r="N5" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1220,7 +3068,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1229,7 +3077,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1238,18 +3086,18 @@
         <v>5</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1258,7 +3106,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1267,7 +3115,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1276,18 +3124,18 @@
         <v>6</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1296,7 +3144,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1305,7 +3153,7 @@
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1314,18 +3162,18 @@
         <v>7</v>
       </c>
       <c r="N8" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1334,7 +3182,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1343,7 +3191,7 @@
         <v>8</v>
       </c>
       <c r="J9" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1352,18 +3200,18 @@
         <v>8</v>
       </c>
       <c r="N9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1372,7 +3220,7 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1381,7 +3229,7 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1390,18 +3238,18 @@
         <v>9</v>
       </c>
       <c r="N10" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1410,7 +3258,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1419,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1428,18 +3276,18 @@
         <v>10</v>
       </c>
       <c r="N11" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1448,7 +3296,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1457,7 +3305,7 @@
         <v>11</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1466,18 +3314,18 @@
         <v>11</v>
       </c>
       <c r="N12" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1486,7 +3334,7 @@
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1495,7 +3343,7 @@
         <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1504,18 +3352,18 @@
         <v>12</v>
       </c>
       <c r="N13" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1524,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1533,7 +3381,7 @@
         <v>13</v>
       </c>
       <c r="J14" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1542,18 +3390,18 @@
         <v>13</v>
       </c>
       <c r="N14" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1562,7 +3410,7 @@
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1571,7 +3419,7 @@
         <v>14</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1580,18 +3428,18 @@
         <v>14</v>
       </c>
       <c r="N15" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1600,7 +3448,7 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1609,7 +3457,7 @@
         <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1618,18 +3466,18 @@
         <v>15</v>
       </c>
       <c r="N16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1638,7 +3486,7 @@
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1647,7 +3495,7 @@
         <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -1656,18 +3504,18 @@
         <v>16</v>
       </c>
       <c r="N17" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1676,7 +3524,7 @@
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1685,7 +3533,7 @@
         <v>17</v>
       </c>
       <c r="J18" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1694,18 +3542,18 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1714,7 +3562,7 @@
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1723,7 +3571,7 @@
         <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -1732,18 +3580,18 @@
         <v>18</v>
       </c>
       <c r="N19" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1752,7 +3600,7 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1761,7 +3609,7 @@
         <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -1770,18 +3618,18 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1790,7 +3638,7 @@
         <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1799,7 +3647,7 @@
         <v>20</v>
       </c>
       <c r="J21" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -1808,18 +3656,18 @@
         <v>20</v>
       </c>
       <c r="N21" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1828,7 +3676,7 @@
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1837,7 +3685,7 @@
         <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -1846,18 +3694,18 @@
         <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1866,7 +3714,7 @@
         <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1875,7 +3723,7 @@
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -1884,18 +3732,18 @@
         <v>22</v>
       </c>
       <c r="N23" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1904,7 +3752,7 @@
         <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1913,7 +3761,7 @@
         <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -1922,18 +3770,18 @@
         <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1942,7 +3790,7 @@
         <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1951,7 +3799,7 @@
         <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -1960,18 +3808,18 @@
         <v>24</v>
       </c>
       <c r="N25" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1980,7 +3828,7 @@
         <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1989,7 +3837,7 @@
         <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -1998,18 +3846,18 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2018,7 +3866,7 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2027,7 +3875,7 @@
         <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2036,18 +3884,18 @@
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2056,7 +3904,7 @@
         <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2065,7 +3913,7 @@
         <v>27</v>
       </c>
       <c r="J28" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2074,18 +3922,18 @@
         <v>27</v>
       </c>
       <c r="N28" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2094,7 +3942,7 @@
         <v>28</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2103,7 +3951,7 @@
         <v>28</v>
       </c>
       <c r="J29" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2112,18 +3960,18 @@
         <v>28</v>
       </c>
       <c r="N29" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2132,7 +3980,7 @@
         <v>29</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2141,7 +3989,7 @@
         <v>29</v>
       </c>
       <c r="J30" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2150,18 +3998,18 @@
         <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2170,7 +4018,7 @@
         <v>30</v>
       </c>
       <c r="F31" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2179,7 +4027,7 @@
         <v>30</v>
       </c>
       <c r="J31" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2188,7 +4036,7 @@
         <v>30</v>
       </c>
       <c r="N31" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O31">
         <v>1</v>
@@ -2200,6 +4048,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B011C3FEFFEFCF44990405A8404263A2" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dc4baf5bca6f50981051f1202939c23">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1497dbabdd8844cfa90d09d2bdc2ce45" ns2:_="">
     <xsd:import namespace="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
@@ -2343,15 +4200,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2359,13 +4207,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD37445E-AC8E-4C0F-AFFA-0F458B30C514}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99F7A0B0-9FF5-43CF-849A-CDB9D64B95B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99F7A0B0-9FF5-43CF-849A-CDB9D64B95B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD37445E-AC8E-4C0F-AFFA-0F458B30C514}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA754AA5-6642-4723-BBB0-BBFCC75ACFFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA754AA5-6642-4723-BBB0-BBFCC75ACFFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>